--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.53985915399801</v>
+        <v>3.825227112524677</v>
       </c>
       <c r="D2" t="n">
-        <v>24.37187554224297</v>
+        <v>3.960429775614482</v>
       </c>
       <c r="E2" t="n">
-        <v>5.817538938609395</v>
+        <v>0.9453500775240268</v>
       </c>
       <c r="F2" t="n">
-        <v>5.894977350765929</v>
+        <v>0.9579338194994635</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.18778923565243</v>
+        <v>2.30551575079352</v>
       </c>
       <c r="D3" t="n">
-        <v>14.53080106530658</v>
+        <v>2.361255173112319</v>
       </c>
       <c r="E3" t="n">
-        <v>5.817538938609395</v>
+        <v>0.9453500775240268</v>
       </c>
       <c r="F3" t="n">
-        <v>5.894977350765929</v>
+        <v>0.9579338194994635</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.5524865872714</v>
+        <v>1.552279070431603</v>
       </c>
       <c r="D4" t="n">
-        <v>10.30019899209679</v>
+        <v>1.673782336215728</v>
       </c>
       <c r="E4" t="n">
-        <v>5.817538938609395</v>
+        <v>0.9453500775240268</v>
       </c>
       <c r="F4" t="n">
-        <v>5.894977350765929</v>
+        <v>0.9579338194994635</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
